--- a/data/export/2026-10-29-operations.xlsx
+++ b/data/export/2026-10-29-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1435,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:25</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1538,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1654,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1770,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1886,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2002,35 +2002,35 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2063,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2118,35 +2118,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -2247,22 +2247,22 @@
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2314,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2466,35 +2466,35 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,35 +2582,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2698,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2778,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2814,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,7 +2930,3487 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-operations.xlsx
+++ b/data/export/2026-10-29-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2131,22 +2131,22 @@
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2234,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2314,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2350,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,35 +2466,35 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2527,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2546,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,35 +2582,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2662,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2698,35 +2698,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2759,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2778,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2814,35 +2814,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2930,35 +2930,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +2991,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3010,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3046,35 +3046,35 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -3175,22 +3175,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3223,12 +3223,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3339,12 +3339,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3358,7 +3358,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3510,7 +3510,7 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3571,12 +3571,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3687,12 +3687,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3755,22 +3755,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3803,12 +3803,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3974,7 +3974,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4035,12 +4035,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4219,22 +4219,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4335,22 +4335,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4438,35 +4438,35 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4499,12 +4499,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4518,7 +4518,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4554,35 +4554,35 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4670,35 +4670,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4786,35 +4786,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4847,12 +4847,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4902,35 +4902,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5018,35 +5018,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5134,35 +5134,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5250,35 +5250,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5366,35 +5366,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5482,35 +5482,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5598,35 +5598,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5714,35 +5714,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5830,35 +5830,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5946,35 +5946,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6062,35 +6062,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6178,35 +6178,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6294,35 +6294,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6410,7 +6410,3371 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-29-operations.xlsx
+++ b/data/export/2026-10-29-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A1:AD101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3059,22 +3059,22 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3169,28 +3169,28 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3223,12 +3223,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3278,35 +3278,35 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3339,12 +3339,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3358,7 +3358,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3394,35 +3394,35 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3510,35 +3510,35 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3571,12 +3571,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3626,35 +3626,35 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3687,12 +3687,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3803,12 +3803,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4035,12 +4035,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4219,22 +4219,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4335,7 +4335,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4499,12 +4499,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4518,7 +4518,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4847,12 +4847,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
           <t>07:11</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>07:41</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5263,7 +5263,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
           <t>07:11</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>07:31</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5379,7 +5379,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5611,22 +5611,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5727,22 +5727,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5959,22 +5959,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
           <t>07:51</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>08:11</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6075,22 +6075,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
           <t>08:02</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6307,7 +6307,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6423,22 +6423,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6490,7 +6490,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6539,22 +6539,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6655,22 +6655,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6765,28 +6765,28 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -6874,35 +6874,35 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6954,7 +6954,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -6990,35 +6990,35 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7070,7 +7070,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7106,35 +7106,35 @@
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7222,35 +7222,35 @@
       <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7338,35 +7338,35 @@
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7454,35 +7454,35 @@
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7570,35 +7570,35 @@
       <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7686,35 +7686,35 @@
       <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7802,35 +7802,35 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -7918,35 +7918,35 @@
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8034,35 +8034,35 @@
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8163,22 +8163,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
@@ -8279,7 +8279,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8346,7 +8346,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8395,22 +8395,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8511,22 +8511,22 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8627,7 +8627,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8694,7 +8694,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -8859,22 +8859,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:09</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -8975,22 +8975,22 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9091,22 +9091,22 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
@@ -9207,22 +9207,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9274,7 +9274,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9323,22 +9323,22 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9371,12 +9371,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9439,22 +9439,22 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9555,22 +9555,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9671,7 +9671,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
@@ -9773,6 +9773,2442 @@
       </c>
       <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-29-operations.xlsx
+++ b/data/export/2026-10-29-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD101"/>
+  <dimension ref="A1:AD110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3639,22 +3639,22 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3749,28 +3749,28 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3803,12 +3803,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3858,35 +3858,35 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -3974,35 +3974,35 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4035,12 +4035,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -4103,22 +4103,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4219,22 +4219,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:36</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4335,7 +4335,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4518,7 +4518,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4683,22 +4683,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4847,12 +4847,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5147,22 +5147,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5263,22 +5263,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5379,7 +5379,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5727,22 +5727,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5843,22 +5843,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6075,7 +6075,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6191,22 +6191,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6307,7 +6307,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6423,22 +6423,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
           <t>07:51</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>08:11</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6490,7 +6490,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6539,7 +6539,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
           <t>08:02</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6771,22 +6771,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6887,22 +6887,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
           <t>08:11</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>08:41</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6954,7 +6954,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7003,22 +7003,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7070,7 +7070,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7119,22 +7119,22 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7235,22 +7235,22 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -7351,22 +7351,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7467,22 +7467,22 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7583,7 +7583,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7699,7 +7699,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7815,22 +7815,22 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -7931,7 +7931,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -7979,7 +7979,7 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8095,7 +8095,7 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8157,28 +8157,28 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8266,35 +8266,35 @@
       <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8346,7 +8346,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8382,35 +8382,35 @@
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8498,35 +8498,35 @@
       <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8614,35 +8614,35 @@
       <c r="AC70" s="2" t="inlineStr"/>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8694,7 +8694,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8730,35 +8730,35 @@
       <c r="AC71" s="2" t="inlineStr"/>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8846,7 +8846,7 @@
       <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -8975,22 +8975,22 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
@@ -9207,7 +9207,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9274,7 +9274,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9323,22 +9323,22 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9371,12 +9371,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9555,22 +9555,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9671,22 +9671,22 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
@@ -9787,22 +9787,22 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -9903,22 +9903,22 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10019,22 +10019,22 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10086,7 +10086,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10202,7 +10202,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
@@ -10367,7 +10367,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10415,12 +10415,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10434,7 +10434,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
@@ -10483,22 +10483,22 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10550,7 +10550,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10599,22 +10599,22 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
@@ -10715,7 +10715,7 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
           <t>07:51</t>
-        </is>
-      </c>
-      <c r="P89" s="2" t="inlineStr">
-        <is>
-          <t>08:32</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
@@ -10831,22 +10831,22 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A53062D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10898,7 +10898,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
@@ -10947,22 +10947,22 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
@@ -11063,22 +11063,22 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
@@ -11295,7 +11295,7 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11362,7 +11362,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
@@ -11411,22 +11411,22 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
@@ -11527,7 +11527,7 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -11575,12 +11575,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11594,7 +11594,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -11643,22 +11643,22 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11710,7 +11710,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -11759,22 +11759,22 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
@@ -11875,22 +11875,22 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11923,12 +11923,12 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -11991,22 +11991,22 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -12039,12 +12039,12 @@
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12058,7 +12058,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
@@ -12107,7 +12107,7 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12174,7 +12174,7 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
@@ -12209,6 +12209,1050 @@
       </c>
       <c r="AC101" s="2" t="inlineStr"/>
       <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr"/>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr"/>
+      <c r="AD105" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr"/>
+      <c r="AD106" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr"/>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr"/>
+      <c r="AD107" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr"/>
+      <c r="AD108" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr"/>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr"/>
+      <c r="AD109" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr"/>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr"/>
+      <c r="AD110" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-29-operations.xlsx
+++ b/data/export/2026-10-29-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD110"/>
+  <dimension ref="A1:AD123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3987,22 +3987,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4035,12 +4035,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4097,28 +4097,28 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4206,35 +4206,35 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4286,7 +4286,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4322,35 +4322,35 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4438,35 +4438,35 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4499,12 +4499,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4518,7 +4518,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4554,35 +4554,35 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5147,22 +5147,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5263,7 +5263,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5379,7 +5379,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5727,7 +5727,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6075,7 +6075,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6307,7 +6307,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6490,7 +6490,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6539,22 +6539,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6655,22 +6655,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -6887,22 +6887,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6954,7 +6954,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7003,22 +7003,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7070,7 +7070,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
           <t>08:02</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>08:29</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7351,22 +7351,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7467,22 +7467,22 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7583,22 +7583,22 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7699,22 +7699,22 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7815,22 +7815,22 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -7931,7 +7931,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8163,22 +8163,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8279,22 +8279,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8346,7 +8346,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8395,7 +8395,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8511,22 +8511,22 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8627,22 +8627,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8694,7 +8694,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8853,28 +8853,28 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -8962,35 +8962,35 @@
       <c r="AC73" s="2" t="inlineStr"/>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9078,35 +9078,35 @@
       <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
@@ -9194,35 +9194,35 @@
       <c r="AC75" s="2" t="inlineStr"/>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9274,7 +9274,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9310,35 +9310,35 @@
       <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9371,12 +9371,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
@@ -9426,35 +9426,35 @@
       <c r="AC77" s="2" t="inlineStr"/>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9542,35 +9542,35 @@
       <c r="AC78" s="2" t="inlineStr"/>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9658,35 +9658,35 @@
       <c r="AC79" s="2" t="inlineStr"/>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9774,35 +9774,35 @@
       <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -9890,35 +9890,35 @@
       <c r="AC81" s="2" t="inlineStr"/>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10006,7 +10006,7 @@
       <c r="AC82" s="2" t="inlineStr"/>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10086,7 +10086,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10202,7 +10202,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
@@ -10251,22 +10251,22 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
@@ -10367,22 +10367,22 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10415,12 +10415,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10434,7 +10434,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
@@ -10483,7 +10483,7 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10550,7 +10550,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
@@ -10599,7 +10599,7 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -10715,22 +10715,22 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
@@ -10831,22 +10831,22 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10898,7 +10898,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
@@ -10947,22 +10947,22 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>08:09</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
@@ -11063,22 +11063,22 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11295,22 +11295,22 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11362,7 +11362,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
@@ -11411,7 +11411,7 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
@@ -11527,22 +11527,22 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11575,12 +11575,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11594,7 +11594,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
@@ -11643,22 +11643,22 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11710,7 +11710,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -11759,22 +11759,22 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11807,7 +11807,7 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
@@ -11875,22 +11875,22 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11923,12 +11923,12 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -11991,22 +11991,22 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A53062D</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -12039,12 +12039,12 @@
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12058,7 +12058,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
@@ -12107,22 +12107,22 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12174,7 +12174,7 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
@@ -12223,22 +12223,22 @@
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -12271,12 +12271,12 @@
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
@@ -12339,22 +12339,22 @@
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -12387,12 +12387,12 @@
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12406,7 +12406,7 @@
       <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
@@ -12455,22 +12455,22 @@
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12503,12 +12503,12 @@
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
@@ -12571,7 +12571,7 @@
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12638,7 +12638,7 @@
       <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
@@ -12687,22 +12687,22 @@
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -12735,12 +12735,12 @@
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
@@ -12803,22 +12803,22 @@
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12870,7 +12870,7 @@
       <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
@@ -12919,22 +12919,22 @@
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -12967,12 +12967,12 @@
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12986,7 +12986,7 @@
       <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
@@ -13035,22 +13035,22 @@
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13102,7 +13102,7 @@
       <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
@@ -13151,22 +13151,22 @@
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -13199,12 +13199,12 @@
       <c r="N110" s="2" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -13218,7 +13218,7 @@
       <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB110" s="2" t="inlineStr">
@@ -13253,6 +13253,1514 @@
       </c>
       <c r="AC110" s="2" t="inlineStr"/>
       <c r="AD110" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr"/>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr"/>
+      <c r="S111" s="2" t="inlineStr"/>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z111" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA111" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB111" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC111" s="2" t="inlineStr"/>
+      <c r="AD111" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr"/>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr"/>
+      <c r="S112" s="2" t="inlineStr"/>
+      <c r="T112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W112" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X112" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y112" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z112" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA112" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB112" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC112" s="2" t="inlineStr"/>
+      <c r="AD112" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr"/>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr"/>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr"/>
+      <c r="S113" s="2" t="inlineStr"/>
+      <c r="T113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X113" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y113" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z113" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA113" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB113" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC113" s="2" t="inlineStr"/>
+      <c r="AD113" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr"/>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr"/>
+      <c r="S114" s="2" t="inlineStr"/>
+      <c r="T114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="W114" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X114" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y114" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z114" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA114" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB114" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC114" s="2" t="inlineStr"/>
+      <c r="AD114" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr"/>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr"/>
+      <c r="S115" s="2" t="inlineStr"/>
+      <c r="T115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X115" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y115" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z115" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA115" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB115" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC115" s="2" t="inlineStr"/>
+      <c r="AD115" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr"/>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr"/>
+      <c r="S116" s="2" t="inlineStr"/>
+      <c r="T116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W116" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z116" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA116" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB116" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC116" s="2" t="inlineStr"/>
+      <c r="AD116" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr"/>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr"/>
+      <c r="S117" s="2" t="inlineStr"/>
+      <c r="T117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W117" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X117" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y117" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z117" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA117" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB117" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC117" s="2" t="inlineStr"/>
+      <c r="AD117" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr"/>
+      <c r="S118" s="2" t="inlineStr"/>
+      <c r="T118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W118" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z118" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA118" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB118" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC118" s="2" t="inlineStr"/>
+      <c r="AD118" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr"/>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr"/>
+      <c r="S119" s="2" t="inlineStr"/>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z119" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA119" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB119" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC119" s="2" t="inlineStr"/>
+      <c r="AD119" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr"/>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr"/>
+      <c r="S120" s="2" t="inlineStr"/>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z120" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA120" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB120" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC120" s="2" t="inlineStr"/>
+      <c r="AD120" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr"/>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr"/>
+      <c r="S121" s="2" t="inlineStr"/>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W121" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z121" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA121" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB121" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC121" s="2" t="inlineStr"/>
+      <c r="AD121" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr"/>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr"/>
+      <c r="S122" s="2" t="inlineStr"/>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W122" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z122" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA122" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB122" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr"/>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr"/>
+      <c r="S123" s="2" t="inlineStr"/>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z123" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA123" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB123" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC123" s="2" t="inlineStr"/>
+      <c r="AD123" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-29-operations.xlsx
+++ b/data/export/2026-10-29-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD123"/>
+  <dimension ref="A1:AD144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4677,28 +4677,28 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4786,35 +4786,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4847,12 +4847,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4902,35 +4902,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5018,35 +5018,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5134,35 +5134,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5250,7 +5250,7 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5379,7 +5379,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5727,22 +5727,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6075,7 +6075,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6307,7 +6307,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6490,7 +6490,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6539,7 +6539,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6954,7 +6954,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7070,7 +7070,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7119,22 +7119,22 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7235,22 +7235,22 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7467,22 +7467,22 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7583,22 +7583,22 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7699,7 +7699,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -7931,22 +7931,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8047,22 +8047,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8163,22 +8163,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
@@ -8279,22 +8279,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8346,7 +8346,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8395,22 +8395,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8627,7 +8627,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8694,7 +8694,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8743,22 +8743,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -8859,22 +8859,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9091,22 +9091,22 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9207,22 +9207,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9274,7 +9274,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9323,7 +9323,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9371,12 +9371,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
@@ -9555,22 +9555,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9671,22 +9671,22 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9787,22 +9787,22 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -9903,22 +9903,22 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10013,28 +10013,28 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10086,7 +10086,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10122,35 +10122,35 @@
       <c r="AC83" s="2" t="inlineStr"/>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10202,7 +10202,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
@@ -10238,35 +10238,35 @@
       <c r="AC84" s="2" t="inlineStr"/>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
@@ -10354,35 +10354,35 @@
       <c r="AC85" s="2" t="inlineStr"/>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10415,12 +10415,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10434,7 +10434,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
@@ -10470,35 +10470,35 @@
       <c r="AC86" s="2" t="inlineStr"/>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10550,7 +10550,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
@@ -10586,35 +10586,35 @@
       <c r="AC87" s="2" t="inlineStr"/>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -10702,35 +10702,35 @@
       <c r="AC88" s="2" t="inlineStr"/>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
@@ -10818,35 +10818,35 @@
       <c r="AC89" s="2" t="inlineStr"/>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10898,7 +10898,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
@@ -10934,35 +10934,35 @@
       <c r="AC90" s="2" t="inlineStr"/>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11050,35 +11050,35 @@
       <c r="AC91" s="2" t="inlineStr"/>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
@@ -11166,35 +11166,35 @@
       <c r="AC92" s="2" t="inlineStr"/>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11282,35 +11282,35 @@
       <c r="AC93" s="2" t="inlineStr"/>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11362,7 +11362,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
@@ -11398,35 +11398,35 @@
       <c r="AC94" s="2" t="inlineStr"/>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
@@ -11514,35 +11514,35 @@
       <c r="AC95" s="2" t="inlineStr"/>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11575,12 +11575,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11594,7 +11594,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
@@ -11630,7 +11630,7 @@
       <c r="AC96" s="2" t="inlineStr"/>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -11643,22 +11643,22 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11710,7 +11710,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -11759,7 +11759,7 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
@@ -11875,22 +11875,22 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
@@ -11991,22 +11991,22 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -12039,12 +12039,12 @@
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12058,7 +12058,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
@@ -12107,7 +12107,7 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12174,7 +12174,7 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -12223,7 +12223,7 @@
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -12271,12 +12271,12 @@
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
@@ -12339,7 +12339,7 @@
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12406,7 +12406,7 @@
       <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
@@ -12455,7 +12455,7 @@
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -12503,12 +12503,12 @@
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
@@ -12571,22 +12571,22 @@
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12638,7 +12638,7 @@
       <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
@@ -12687,7 +12687,7 @@
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -12697,7 +12697,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -12735,12 +12735,12 @@
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
@@ -12803,7 +12803,7 @@
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -12851,12 +12851,12 @@
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12870,7 +12870,7 @@
       <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
@@ -12919,22 +12919,22 @@
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -12967,12 +12967,12 @@
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12986,7 +12986,7 @@
       <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
@@ -13035,22 +13035,22 @@
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13102,7 +13102,7 @@
       <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
@@ -13151,22 +13151,22 @@
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -13199,12 +13199,12 @@
       <c r="N110" s="2" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -13218,7 +13218,7 @@
       <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB110" s="2" t="inlineStr">
@@ -13267,22 +13267,22 @@
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -13334,7 +13334,7 @@
       <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="AA111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB111" s="2" t="inlineStr">
@@ -13383,22 +13383,22 @@
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -13431,12 +13431,12 @@
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -13450,7 +13450,7 @@
       <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W112" s="2" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="AA112" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB112" s="2" t="inlineStr">
@@ -13499,7 +13499,7 @@
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -13509,7 +13509,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -13566,7 +13566,7 @@
       <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
@@ -13615,7 +13615,7 @@
       <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A53062D</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -13682,7 +13682,7 @@
       <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W114" s="2" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="AA114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB114" s="2" t="inlineStr">
@@ -13731,7 +13731,7 @@
       <c r="B115" s="2" t="inlineStr"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -13779,12 +13779,12 @@
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -13798,7 +13798,7 @@
       <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="AA115" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB115" s="2" t="inlineStr">
@@ -13847,7 +13847,7 @@
       <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -13914,7 +13914,7 @@
       <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="AA116" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB116" s="2" t="inlineStr">
@@ -13963,22 +13963,22 @@
       <c r="B117" s="2" t="inlineStr"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14030,7 +14030,7 @@
       <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
@@ -14084,17 +14084,17 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -14146,7 +14146,7 @@
       <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W118" s="2" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="AA118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB118" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       <c r="B119" s="2" t="inlineStr"/>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       <c r="N119" s="2" t="inlineStr"/>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -14262,7 +14262,7 @@
       <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W119" s="2" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="AA119" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB119" s="2" t="inlineStr">
@@ -14311,7 +14311,7 @@
       <c r="B120" s="2" t="inlineStr"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -14359,12 +14359,12 @@
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -14378,7 +14378,7 @@
       <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W120" s="2" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="AA120" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB120" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       <c r="B121" s="2" t="inlineStr"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -14494,7 +14494,7 @@
       <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W121" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="AA121" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB121" s="2" t="inlineStr">
@@ -14543,7 +14543,7 @@
       <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -14591,12 +14591,12 @@
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -14610,7 +14610,7 @@
       <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W122" s="2" t="inlineStr">
@@ -14659,7 +14659,7 @@
       <c r="B123" s="2" t="inlineStr"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -14707,12 +14707,12 @@
       <c r="N123" s="2" t="inlineStr"/>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -14726,7 +14726,7 @@
       <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
@@ -14761,6 +14761,2442 @@
       </c>
       <c r="AC123" s="2" t="inlineStr"/>
       <c r="AD123" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr"/>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr"/>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X124" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z124" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA124" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB124" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC124" s="2" t="inlineStr"/>
+      <c r="AD124" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr"/>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr"/>
+      <c r="S125" s="2" t="inlineStr"/>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z125" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA125" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB125" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC125" s="2" t="inlineStr"/>
+      <c r="AD125" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr"/>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr"/>
+      <c r="S126" s="2" t="inlineStr"/>
+      <c r="T126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X126" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y126" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z126" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA126" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB126" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC126" s="2" t="inlineStr"/>
+      <c r="AD126" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr"/>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr"/>
+      <c r="S127" s="2" t="inlineStr"/>
+      <c r="T127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z127" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA127" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB127" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC127" s="2" t="inlineStr"/>
+      <c r="AD127" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr"/>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr"/>
+      <c r="S128" s="2" t="inlineStr"/>
+      <c r="T128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="W128" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z128" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA128" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB128" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC128" s="2" t="inlineStr"/>
+      <c r="AD128" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr"/>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr"/>
+      <c r="S129" s="2" t="inlineStr"/>
+      <c r="T129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W129" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X129" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y129" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z129" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA129" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB129" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC129" s="2" t="inlineStr"/>
+      <c r="AD129" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr"/>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr"/>
+      <c r="S130" s="2" t="inlineStr"/>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X130" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y130" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z130" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA130" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB130" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC130" s="2" t="inlineStr"/>
+      <c r="AD130" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr"/>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr"/>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr"/>
+      <c r="S131" s="2" t="inlineStr"/>
+      <c r="T131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z131" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA131" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB131" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC131" s="2" t="inlineStr"/>
+      <c r="AD131" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr"/>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr"/>
+      <c r="S132" s="2" t="inlineStr"/>
+      <c r="T132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z132" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA132" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB132" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC132" s="2" t="inlineStr"/>
+      <c r="AD132" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr"/>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr"/>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr"/>
+      <c r="S133" s="2" t="inlineStr"/>
+      <c r="T133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z133" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA133" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB133" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC133" s="2" t="inlineStr"/>
+      <c r="AD133" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr"/>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr"/>
+      <c r="S134" s="2" t="inlineStr"/>
+      <c r="T134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z134" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA134" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB134" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC134" s="2" t="inlineStr"/>
+      <c r="AD134" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr"/>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr"/>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr"/>
+      <c r="S135" s="2" t="inlineStr"/>
+      <c r="T135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X135" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y135" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z135" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA135" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB135" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC135" s="2" t="inlineStr"/>
+      <c r="AD135" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr"/>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr"/>
+      <c r="S136" s="2" t="inlineStr"/>
+      <c r="T136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W136" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z136" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA136" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB136" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC136" s="2" t="inlineStr"/>
+      <c r="AD136" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr"/>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr"/>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr"/>
+      <c r="S137" s="2" t="inlineStr"/>
+      <c r="T137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="W137" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z137" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA137" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB137" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC137" s="2" t="inlineStr"/>
+      <c r="AD137" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr"/>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr"/>
+      <c r="S138" s="2" t="inlineStr"/>
+      <c r="T138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z138" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA138" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB138" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC138" s="2" t="inlineStr"/>
+      <c r="AD138" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr"/>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr"/>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr"/>
+      <c r="S139" s="2" t="inlineStr"/>
+      <c r="T139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="W139" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z139" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA139" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB139" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC139" s="2" t="inlineStr"/>
+      <c r="AD139" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr"/>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr"/>
+      <c r="S140" s="2" t="inlineStr"/>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="W140" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z140" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA140" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB140" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC140" s="2" t="inlineStr"/>
+      <c r="AD140" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr"/>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr"/>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R141" s="2" t="inlineStr"/>
+      <c r="S141" s="2" t="inlineStr"/>
+      <c r="T141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="W141" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z141" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA141" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB141" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC141" s="2" t="inlineStr"/>
+      <c r="AD141" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr"/>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr"/>
+      <c r="S142" s="2" t="inlineStr"/>
+      <c r="T142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z142" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA142" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB142" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC142" s="2" t="inlineStr"/>
+      <c r="AD142" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr"/>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr"/>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr"/>
+      <c r="S143" s="2" t="inlineStr"/>
+      <c r="T143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z143" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA143" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB143" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC143" s="2" t="inlineStr"/>
+      <c r="AD143" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr"/>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr"/>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr"/>
+      <c r="S144" s="2" t="inlineStr"/>
+      <c r="T144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X144" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y144" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z144" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA144" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB144" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC144" s="2" t="inlineStr"/>
+      <c r="AD144" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-29-operations.xlsx
+++ b/data/export/2026-10-29-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD144"/>
+  <dimension ref="A1:AD160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5257,28 +5257,28 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5366,35 +5366,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5482,35 +5482,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5598,35 +5598,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5714,35 +5714,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -5830,35 +5830,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -5946,7 +5946,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -5959,22 +5959,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6075,22 +6075,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6294,7 +6294,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6410,7 +6410,7 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6490,7 +6490,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6539,22 +6539,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6655,22 +6655,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6758,7 +6758,7 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6954,7 +6954,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -6990,7 +6990,7 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7003,22 +7003,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7070,7 +7070,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7119,22 +7119,22 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7222,7 +7222,7 @@
       <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7235,22 +7235,22 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7338,7 +7338,7 @@
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7351,22 +7351,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7454,7 +7454,7 @@
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7570,7 +7570,7 @@
       <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7583,22 +7583,22 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7699,7 +7699,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7802,7 +7802,7 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7931,22 +7931,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8047,22 +8047,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
@@ -8266,7 +8266,7 @@
       <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8346,7 +8346,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8382,7 +8382,7 @@
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8395,22 +8395,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8511,22 +8511,22 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       <c r="AC70" s="2" t="inlineStr"/>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8627,7 +8627,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8694,7 +8694,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8730,7 +8730,7 @@
       <c r="AC71" s="2" t="inlineStr"/>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -8846,7 +8846,7 @@
       <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -8962,7 +8962,7 @@
       <c r="AC73" s="2" t="inlineStr"/>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9078,7 +9078,7 @@
       <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -9091,22 +9091,22 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9194,7 +9194,7 @@
       <c r="AC75" s="2" t="inlineStr"/>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -9207,22 +9207,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9274,7 +9274,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9310,7 +9310,7 @@
       <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9371,12 +9371,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
@@ -9426,7 +9426,7 @@
       <c r="AC77" s="2" t="inlineStr"/>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       <c r="AC78" s="2" t="inlineStr"/>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -9555,22 +9555,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       <c r="AC79" s="2" t="inlineStr"/>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -9671,22 +9671,22 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -9787,7 +9787,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -9890,7 +9890,7 @@
       <c r="AC81" s="2" t="inlineStr"/>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10006,7 +10006,7 @@
       <c r="AC82" s="2" t="inlineStr"/>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -10019,22 +10019,22 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10086,7 +10086,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
@@ -10122,7 +10122,7 @@
       <c r="AC83" s="2" t="inlineStr"/>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -10135,22 +10135,22 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10202,7 +10202,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
@@ -10238,7 +10238,7 @@
       <c r="AC84" s="2" t="inlineStr"/>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -10251,7 +10251,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       <c r="AC85" s="2" t="inlineStr"/>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10367,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10415,12 +10415,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10434,7 +10434,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10470,7 +10470,7 @@
       <c r="AC86" s="2" t="inlineStr"/>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10483,7 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10550,7 +10550,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       <c r="AC87" s="2" t="inlineStr"/>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
@@ -10702,7 +10702,7 @@
       <c r="AC88" s="2" t="inlineStr"/>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -10715,22 +10715,22 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -10818,7 +10818,7 @@
       <c r="AC89" s="2" t="inlineStr"/>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -10831,22 +10831,22 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10898,7 +10898,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -10934,7 +10934,7 @@
       <c r="AC90" s="2" t="inlineStr"/>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -10947,22 +10947,22 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11050,7 +11050,7 @@
       <c r="AC91" s="2" t="inlineStr"/>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -11063,22 +11063,22 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
@@ -11166,7 +11166,7 @@
       <c r="AC92" s="2" t="inlineStr"/>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -11179,22 +11179,22 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
@@ -11282,7 +11282,7 @@
       <c r="AC93" s="2" t="inlineStr"/>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -11295,22 +11295,22 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11362,7 +11362,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
@@ -11398,7 +11398,7 @@
       <c r="AC94" s="2" t="inlineStr"/>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -11411,7 +11411,7 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
@@ -11514,7 +11514,7 @@
       <c r="AC95" s="2" t="inlineStr"/>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -11575,12 +11575,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11594,7 +11594,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
@@ -11630,35 +11630,35 @@
       <c r="AC96" s="2" t="inlineStr"/>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11710,7 +11710,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -11746,35 +11746,35 @@
       <c r="AC97" s="2" t="inlineStr"/>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
@@ -11862,35 +11862,35 @@
       <c r="AC98" s="2" t="inlineStr"/>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
@@ -11978,35 +11978,35 @@
       <c r="AC99" s="2" t="inlineStr"/>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -12039,12 +12039,12 @@
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12058,7 +12058,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
@@ -12094,35 +12094,35 @@
       <c r="AC100" s="2" t="inlineStr"/>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12174,7 +12174,7 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -12210,35 +12210,35 @@
       <c r="AC101" s="2" t="inlineStr"/>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -12271,12 +12271,12 @@
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
@@ -12326,35 +12326,35 @@
       <c r="AC102" s="2" t="inlineStr"/>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -12387,12 +12387,12 @@
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12406,7 +12406,7 @@
       <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
@@ -12442,35 +12442,35 @@
       <c r="AC103" s="2" t="inlineStr"/>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12503,12 +12503,12 @@
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
@@ -12558,35 +12558,35 @@
       <c r="AC104" s="2" t="inlineStr"/>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12638,7 +12638,7 @@
       <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
@@ -12674,35 +12674,35 @@
       <c r="AC105" s="2" t="inlineStr"/>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -12735,12 +12735,12 @@
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
@@ -12790,35 +12790,35 @@
       <c r="AC106" s="2" t="inlineStr"/>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12851,12 +12851,12 @@
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12870,7 +12870,7 @@
       <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
@@ -12906,7 +12906,7 @@
       <c r="AC107" s="2" t="inlineStr"/>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -12919,7 +12919,7 @@
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -12967,12 +12967,12 @@
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12986,7 +12986,7 @@
       <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="AA108" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB108" s="2" t="inlineStr">
@@ -13035,22 +13035,22 @@
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13102,7 +13102,7 @@
       <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB109" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -13199,12 +13199,12 @@
       <c r="N110" s="2" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -13218,7 +13218,7 @@
       <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB110" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -13315,12 +13315,12 @@
       <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -13334,7 +13334,7 @@
       <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="AA111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB111" s="2" t="inlineStr">
@@ -13383,22 +13383,22 @@
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -13431,12 +13431,12 @@
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -13450,7 +13450,7 @@
       <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W112" s="2" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="AA112" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB112" s="2" t="inlineStr">
@@ -13499,22 +13499,22 @@
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -13566,7 +13566,7 @@
       <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
@@ -13615,7 +13615,7 @@
       <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -13682,7 +13682,7 @@
       <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W114" s="2" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="AA114" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB114" s="2" t="inlineStr">
@@ -13731,7 +13731,7 @@
       <c r="B115" s="2" t="inlineStr"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -13779,12 +13779,12 @@
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -13798,7 +13798,7 @@
       <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
@@ -13847,7 +13847,7 @@
       <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -13914,7 +13914,7 @@
       <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="AA116" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB116" s="2" t="inlineStr">
@@ -13963,22 +13963,22 @@
       <c r="B117" s="2" t="inlineStr"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14030,7 +14030,7 @@
       <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
@@ -14079,22 +14079,22 @@
       <c r="B118" s="2" t="inlineStr"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -14127,12 +14127,12 @@
       <c r="N118" s="2" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -14146,7 +14146,7 @@
       <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W118" s="2" t="inlineStr">
@@ -14195,22 +14195,22 @@
       <c r="B119" s="2" t="inlineStr"/>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       <c r="N119" s="2" t="inlineStr"/>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -14262,7 +14262,7 @@
       <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W119" s="2" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="AA119" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB119" s="2" t="inlineStr">
@@ -14311,7 +14311,7 @@
       <c r="B120" s="2" t="inlineStr"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -14359,12 +14359,12 @@
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -14378,7 +14378,7 @@
       <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W120" s="2" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="AA120" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB120" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       <c r="B121" s="2" t="inlineStr"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -14475,12 +14475,12 @@
       <c r="N121" s="2" t="inlineStr"/>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -14494,7 +14494,7 @@
       <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W121" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="AA121" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB121" s="2" t="inlineStr">
@@ -14543,7 +14543,7 @@
       <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -14591,12 +14591,12 @@
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -14610,7 +14610,7 @@
       <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W122" s="2" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="AA122" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB122" s="2" t="inlineStr">
@@ -14659,7 +14659,7 @@
       <c r="B123" s="2" t="inlineStr"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -14707,12 +14707,12 @@
       <c r="N123" s="2" t="inlineStr"/>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -14726,7 +14726,7 @@
       <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="AA123" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB123" s="2" t="inlineStr">
@@ -14775,7 +14775,7 @@
       <c r="B124" s="2" t="inlineStr"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -14785,7 +14785,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -14823,12 +14823,12 @@
       <c r="N124" s="2" t="inlineStr"/>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -14842,7 +14842,7 @@
       <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="W124" s="2" t="inlineStr">
@@ -14891,7 +14891,7 @@
       <c r="B125" s="2" t="inlineStr"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A53062D</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -14939,12 +14939,12 @@
       <c r="N125" s="2" t="inlineStr"/>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -14958,7 +14958,7 @@
       <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W125" s="2" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="AA125" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB125" s="2" t="inlineStr">
@@ -15007,7 +15007,7 @@
       <c r="B126" s="2" t="inlineStr"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -15055,12 +15055,12 @@
       <c r="N126" s="2" t="inlineStr"/>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -15074,7 +15074,7 @@
       <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="W126" s="2" t="inlineStr">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="AA126" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB126" s="2" t="inlineStr">
@@ -15123,22 +15123,22 @@
       <c r="B127" s="2" t="inlineStr"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       <c r="N127" s="2" t="inlineStr"/>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -15190,7 +15190,7 @@
       <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W127" s="2" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="AA127" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB127" s="2" t="inlineStr">
@@ -15239,7 +15239,7 @@
       <c r="B128" s="2" t="inlineStr"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -15287,12 +15287,12 @@
       <c r="N128" s="2" t="inlineStr"/>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -15306,7 +15306,7 @@
       <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W128" s="2" t="inlineStr">
@@ -15355,7 +15355,7 @@
       <c r="B129" s="2" t="inlineStr"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -15403,12 +15403,12 @@
       <c r="N129" s="2" t="inlineStr"/>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -15422,7 +15422,7 @@
       <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W129" s="2" t="inlineStr">
@@ -15447,7 +15447,7 @@
       </c>
       <c r="AA129" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB129" s="2" t="inlineStr">
@@ -15471,22 +15471,22 @@
       <c r="B130" s="2" t="inlineStr"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -15519,12 +15519,12 @@
       <c r="N130" s="2" t="inlineStr"/>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -15538,7 +15538,7 @@
       <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="AA130" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB130" s="2" t="inlineStr">
@@ -15587,7 +15587,7 @@
       <c r="B131" s="2" t="inlineStr"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -15635,12 +15635,12 @@
       <c r="N131" s="2" t="inlineStr"/>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -15654,7 +15654,7 @@
       <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W131" s="2" t="inlineStr">
@@ -15679,7 +15679,7 @@
       </c>
       <c r="AA131" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB131" s="2" t="inlineStr">
@@ -15703,7 +15703,7 @@
       <c r="B132" s="2" t="inlineStr"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -15751,12 +15751,12 @@
       <c r="N132" s="2" t="inlineStr"/>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -15770,7 +15770,7 @@
       <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
@@ -15819,7 +15819,7 @@
       <c r="B133" s="2" t="inlineStr"/>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -15872,7 +15872,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -15886,7 +15886,7 @@
       <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W133" s="2" t="inlineStr">
@@ -15911,7 +15911,7 @@
       </c>
       <c r="AA133" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB133" s="2" t="inlineStr">
@@ -15935,22 +15935,22 @@
       <c r="B134" s="2" t="inlineStr"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -15983,12 +15983,12 @@
       <c r="N134" s="2" t="inlineStr"/>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -16002,7 +16002,7 @@
       <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W134" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="AA134" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB134" s="2" t="inlineStr">
@@ -16051,22 +16051,22 @@
       <c r="B135" s="2" t="inlineStr"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16099,12 +16099,12 @@
       <c r="N135" s="2" t="inlineStr"/>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -16118,7 +16118,7 @@
       <c r="U135" s="2" t="inlineStr"/>
       <c r="V135" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W135" s="2" t="inlineStr">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="AA135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB135" s="2" t="inlineStr">
@@ -16167,22 +16167,22 @@
       <c r="B136" s="2" t="inlineStr"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16215,12 +16215,12 @@
       <c r="N136" s="2" t="inlineStr"/>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -16234,7 +16234,7 @@
       <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W136" s="2" t="inlineStr">
@@ -16259,7 +16259,7 @@
       </c>
       <c r="AA136" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB136" s="2" t="inlineStr">
@@ -16283,7 +16283,7 @@
       <c r="B137" s="2" t="inlineStr"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -16350,7 +16350,7 @@
       <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W137" s="2" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="AA137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB137" s="2" t="inlineStr">
@@ -16399,22 +16399,22 @@
       <c r="B138" s="2" t="inlineStr"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16447,12 +16447,12 @@
       <c r="N138" s="2" t="inlineStr"/>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -16466,7 +16466,7 @@
       <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W138" s="2" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="AA138" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB138" s="2" t="inlineStr">
@@ -16520,17 +16520,17 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -16582,7 +16582,7 @@
       <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="W139" s="2" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="AA139" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB139" s="2" t="inlineStr">
@@ -16631,22 +16631,22 @@
       <c r="B140" s="2" t="inlineStr"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16679,12 +16679,12 @@
       <c r="N140" s="2" t="inlineStr"/>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -16698,7 +16698,7 @@
       <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W140" s="2" t="inlineStr">
@@ -16723,7 +16723,7 @@
       </c>
       <c r="AA140" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB140" s="2" t="inlineStr">
@@ -16752,17 +16752,17 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -16814,7 +16814,7 @@
       <c r="U141" s="2" t="inlineStr"/>
       <c r="V141" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W141" s="2" t="inlineStr">
@@ -16868,17 +16868,17 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -16930,7 +16930,7 @@
       <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W142" s="2" t="inlineStr">
@@ -16984,17 +16984,17 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -17046,7 +17046,7 @@
       <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W143" s="2" t="inlineStr">
@@ -17095,22 +17095,22 @@
       <c r="B144" s="2" t="inlineStr"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -17162,7 +17162,7 @@
       <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W144" s="2" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="AA144" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB144" s="2" t="inlineStr">
@@ -17197,6 +17197,1862 @@
       </c>
       <c r="AC144" s="2" t="inlineStr"/>
       <c r="AD144" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr"/>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr"/>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr"/>
+      <c r="S145" s="2" t="inlineStr"/>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="W145" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X145" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y145" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z145" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA145" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB145" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC145" s="2" t="inlineStr"/>
+      <c r="AD145" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr"/>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr"/>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr"/>
+      <c r="S146" s="2" t="inlineStr"/>
+      <c r="T146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W146" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z146" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA146" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB146" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC146" s="2" t="inlineStr"/>
+      <c r="AD146" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr"/>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr"/>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr"/>
+      <c r="S147" s="2" t="inlineStr"/>
+      <c r="T147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W147" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z147" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA147" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB147" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC147" s="2" t="inlineStr"/>
+      <c r="AD147" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr"/>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr"/>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr"/>
+      <c r="S148" s="2" t="inlineStr"/>
+      <c r="T148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z148" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA148" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB148" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC148" s="2" t="inlineStr"/>
+      <c r="AD148" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr"/>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr"/>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr"/>
+      <c r="S149" s="2" t="inlineStr"/>
+      <c r="T149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z149" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA149" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB149" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC149" s="2" t="inlineStr"/>
+      <c r="AD149" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr"/>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr"/>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr"/>
+      <c r="S150" s="2" t="inlineStr"/>
+      <c r="T150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X150" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y150" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z150" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA150" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB150" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC150" s="2" t="inlineStr"/>
+      <c r="AD150" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr"/>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr"/>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr"/>
+      <c r="S151" s="2" t="inlineStr"/>
+      <c r="T151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z151" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA151" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB151" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC151" s="2" t="inlineStr"/>
+      <c r="AD151" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr"/>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr"/>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr"/>
+      <c r="S152" s="2" t="inlineStr"/>
+      <c r="T152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z152" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA152" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB152" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC152" s="2" t="inlineStr"/>
+      <c r="AD152" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr"/>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr"/>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr"/>
+      <c r="S153" s="2" t="inlineStr"/>
+      <c r="T153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z153" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA153" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB153" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC153" s="2" t="inlineStr"/>
+      <c r="AD153" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr"/>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr"/>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr"/>
+      <c r="S154" s="2" t="inlineStr"/>
+      <c r="T154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z154" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA154" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB154" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC154" s="2" t="inlineStr"/>
+      <c r="AD154" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr"/>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr"/>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr"/>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr"/>
+      <c r="S155" s="2" t="inlineStr"/>
+      <c r="T155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z155" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA155" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB155" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC155" s="2" t="inlineStr"/>
+      <c r="AD155" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr"/>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr"/>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr"/>
+      <c r="S156" s="2" t="inlineStr"/>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="W156" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z156" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA156" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB156" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC156" s="2" t="inlineStr"/>
+      <c r="AD156" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr"/>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr"/>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr"/>
+      <c r="S157" s="2" t="inlineStr"/>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="W157" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X157" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y157" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z157" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA157" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB157" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC157" s="2" t="inlineStr"/>
+      <c r="AD157" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr"/>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr"/>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr"/>
+      <c r="S158" s="2" t="inlineStr"/>
+      <c r="T158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X158" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y158" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z158" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA158" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB158" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC158" s="2" t="inlineStr"/>
+      <c r="AD158" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr"/>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr"/>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr"/>
+      <c r="S159" s="2" t="inlineStr"/>
+      <c r="T159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X159" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y159" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z159" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA159" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB159" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC159" s="2" t="inlineStr"/>
+      <c r="AD159" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr"/>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr"/>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr"/>
+      <c r="S160" s="2" t="inlineStr"/>
+      <c r="T160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z160" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA160" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB160" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC160" s="2" t="inlineStr"/>
+      <c r="AD160" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-29-operations.xlsx
+++ b/data/export/2026-10-29-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD160"/>
+  <dimension ref="A1:AD174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5953,28 +5953,28 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6062,35 +6062,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6142,7 +6142,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6178,35 +6178,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6294,35 +6294,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6410,7 +6410,7 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6490,7 +6490,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6539,22 +6539,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6655,22 +6655,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6771,22 +6771,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6887,22 +6887,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6954,7 +6954,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7003,22 +7003,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7070,7 +7070,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7119,22 +7119,22 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7235,22 +7235,22 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7283,7 +7283,7 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -7351,22 +7351,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7583,22 +7583,22 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7699,22 +7699,22 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7815,22 +7815,22 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -7931,22 +7931,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8163,22 +8163,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8279,22 +8279,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8346,7 +8346,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8395,7 +8395,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8627,7 +8627,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8694,7 +8694,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -8859,22 +8859,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -8975,22 +8975,22 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
           <t>08:02</t>
-        </is>
-      </c>
-      <c r="P74" s="2" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9207,7 +9207,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9274,7 +9274,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9323,7 +9323,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9371,12 +9371,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9555,7 +9555,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9671,7 +9671,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9787,22 +9787,22 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -9903,22 +9903,22 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
@@ -10019,7 +10019,7 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10086,7 +10086,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10202,7 +10202,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10367,7 +10367,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10415,12 +10415,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10434,7 +10434,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10483,22 +10483,22 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10550,7 +10550,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
@@ -10599,22 +10599,22 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -10715,7 +10715,7 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -10831,7 +10831,7 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10898,7 +10898,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -10947,7 +10947,7 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11063,7 +11063,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
@@ -11295,7 +11295,7 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11362,7 +11362,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11411,22 +11411,22 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11527,22 +11527,22 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11575,12 +11575,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11594,7 +11594,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
@@ -11643,22 +11643,22 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11710,7 +11710,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
@@ -11759,22 +11759,22 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -11923,12 +11923,12 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -11991,7 +11991,7 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -12039,12 +12039,12 @@
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12058,7 +12058,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
@@ -12107,7 +12107,7 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12174,7 +12174,7 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -12223,7 +12223,7 @@
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -12271,12 +12271,12 @@
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
@@ -12339,7 +12339,7 @@
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>沪A79307D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -12387,12 +12387,12 @@
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12406,7 +12406,7 @@
       <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
@@ -12455,22 +12455,22 @@
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12503,12 +12503,12 @@
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
@@ -12571,22 +12571,22 @@
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12638,7 +12638,7 @@
       <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
@@ -12687,22 +12687,22 @@
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -12735,7 +12735,7 @@
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
@@ -12803,22 +12803,22 @@
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12851,7 +12851,7 @@
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -12870,7 +12870,7 @@
       <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AA107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB107" s="2" t="inlineStr">
@@ -12913,28 +12913,28 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -12967,12 +12967,12 @@
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12986,7 +12986,7 @@
       <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
@@ -13022,35 +13022,35 @@
       <c r="AC108" s="2" t="inlineStr"/>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13102,7 +13102,7 @@
       <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB109" s="2" t="inlineStr">
@@ -13138,35 +13138,35 @@
       <c r="AC109" s="2" t="inlineStr"/>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -13199,12 +13199,12 @@
       <c r="N110" s="2" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -13218,7 +13218,7 @@
       <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB110" s="2" t="inlineStr">
@@ -13254,35 +13254,35 @@
       <c r="AC110" s="2" t="inlineStr"/>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -13315,12 +13315,12 @@
       <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -13334,7 +13334,7 @@
       <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="AA111" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB111" s="2" t="inlineStr">
@@ -13370,35 +13370,35 @@
       <c r="AC111" s="2" t="inlineStr"/>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -13431,12 +13431,12 @@
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -13450,7 +13450,7 @@
       <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="W112" s="2" t="inlineStr">
@@ -13486,35 +13486,35 @@
       <c r="AC112" s="2" t="inlineStr"/>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -13566,7 +13566,7 @@
       <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="AA113" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB113" s="2" t="inlineStr">
@@ -13602,35 +13602,35 @@
       <c r="AC113" s="2" t="inlineStr"/>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -13682,7 +13682,7 @@
       <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="W114" s="2" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="AA114" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB114" s="2" t="inlineStr">
@@ -13718,35 +13718,35 @@
       <c r="AC114" s="2" t="inlineStr"/>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -13779,12 +13779,12 @@
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -13798,7 +13798,7 @@
       <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="AA115" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB115" s="2" t="inlineStr">
@@ -13834,35 +13834,35 @@
       <c r="AC115" s="2" t="inlineStr"/>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -13914,7 +13914,7 @@
       <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
@@ -13950,7 +13950,7 @@
       <c r="AC116" s="2" t="inlineStr"/>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -13963,22 +13963,22 @@
       <c r="B117" s="2" t="inlineStr"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -14011,12 +14011,12 @@
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14030,7 +14030,7 @@
       <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
@@ -14079,7 +14079,7 @@
       <c r="B118" s="2" t="inlineStr"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -14127,12 +14127,12 @@
       <c r="N118" s="2" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -14146,7 +14146,7 @@
       <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W118" s="2" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="AA118" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB118" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       <c r="B119" s="2" t="inlineStr"/>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       <c r="N119" s="2" t="inlineStr"/>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -14262,7 +14262,7 @@
       <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W119" s="2" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="AA119" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB119" s="2" t="inlineStr">
@@ -14311,7 +14311,7 @@
       <c r="B120" s="2" t="inlineStr"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -14321,7 +14321,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -14359,12 +14359,12 @@
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -14378,7 +14378,7 @@
       <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W120" s="2" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="AA120" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB120" s="2" t="inlineStr">
@@ -14427,22 +14427,22 @@
       <c r="B121" s="2" t="inlineStr"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -14475,12 +14475,12 @@
       <c r="N121" s="2" t="inlineStr"/>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -14494,7 +14494,7 @@
       <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W121" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="AA121" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB121" s="2" t="inlineStr">
@@ -14543,22 +14543,22 @@
       <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -14591,12 +14591,12 @@
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -14610,7 +14610,7 @@
       <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W122" s="2" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="AA122" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB122" s="2" t="inlineStr">
@@ -14659,7 +14659,7 @@
       <c r="B123" s="2" t="inlineStr"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -14707,12 +14707,12 @@
       <c r="N123" s="2" t="inlineStr"/>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -14726,7 +14726,7 @@
       <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="AA123" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB123" s="2" t="inlineStr">
@@ -14775,7 +14775,7 @@
       <c r="B124" s="2" t="inlineStr"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -14785,7 +14785,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -14823,12 +14823,12 @@
       <c r="N124" s="2" t="inlineStr"/>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -14842,7 +14842,7 @@
       <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W124" s="2" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="AA124" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB124" s="2" t="inlineStr">
@@ -14891,7 +14891,7 @@
       <c r="B125" s="2" t="inlineStr"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -14939,12 +14939,12 @@
       <c r="N125" s="2" t="inlineStr"/>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -14958,7 +14958,7 @@
       <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W125" s="2" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="AA125" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB125" s="2" t="inlineStr">
@@ -15007,7 +15007,7 @@
       <c r="B126" s="2" t="inlineStr"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -15055,12 +15055,12 @@
       <c r="N126" s="2" t="inlineStr"/>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -15074,7 +15074,7 @@
       <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W126" s="2" t="inlineStr">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="AA126" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB126" s="2" t="inlineStr">
@@ -15123,7 +15123,7 @@
       <c r="B127" s="2" t="inlineStr"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       <c r="N127" s="2" t="inlineStr"/>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -15190,7 +15190,7 @@
       <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W127" s="2" t="inlineStr">
@@ -15239,7 +15239,7 @@
       <c r="B128" s="2" t="inlineStr"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -15287,12 +15287,12 @@
       <c r="N128" s="2" t="inlineStr"/>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -15306,7 +15306,7 @@
       <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W128" s="2" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="AA128" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB128" s="2" t="inlineStr">
@@ -15355,7 +15355,7 @@
       <c r="B129" s="2" t="inlineStr"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -15403,12 +15403,12 @@
       <c r="N129" s="2" t="inlineStr"/>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -15422,7 +15422,7 @@
       <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W129" s="2" t="inlineStr">
@@ -15471,22 +15471,22 @@
       <c r="B130" s="2" t="inlineStr"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -15519,12 +15519,12 @@
       <c r="N130" s="2" t="inlineStr"/>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -15538,7 +15538,7 @@
       <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
@@ -15587,7 +15587,7 @@
       <c r="B131" s="2" t="inlineStr"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -15635,12 +15635,12 @@
       <c r="N131" s="2" t="inlineStr"/>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -15654,7 +15654,7 @@
       <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W131" s="2" t="inlineStr">
@@ -15679,7 +15679,7 @@
       </c>
       <c r="AA131" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB131" s="2" t="inlineStr">
@@ -15703,7 +15703,7 @@
       <c r="B132" s="2" t="inlineStr"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -15751,12 +15751,12 @@
       <c r="N132" s="2" t="inlineStr"/>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -15770,7 +15770,7 @@
       <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="AA132" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB132" s="2" t="inlineStr">
@@ -15819,7 +15819,7 @@
       <c r="B133" s="2" t="inlineStr"/>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -15867,12 +15867,12 @@
       <c r="N133" s="2" t="inlineStr"/>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -15886,7 +15886,7 @@
       <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="W133" s="2" t="inlineStr">
@@ -15911,7 +15911,7 @@
       </c>
       <c r="AA133" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB133" s="2" t="inlineStr">
@@ -15935,7 +15935,7 @@
       <c r="B134" s="2" t="inlineStr"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A53062D</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -15983,12 +15983,12 @@
       <c r="N134" s="2" t="inlineStr"/>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -16002,7 +16002,7 @@
       <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W134" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="AA134" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB134" s="2" t="inlineStr">
@@ -16051,7 +16051,7 @@
       <c r="B135" s="2" t="inlineStr"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -16099,12 +16099,12 @@
       <c r="N135" s="2" t="inlineStr"/>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -16118,7 +16118,7 @@
       <c r="U135" s="2" t="inlineStr"/>
       <c r="V135" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="W135" s="2" t="inlineStr">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="AA135" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB135" s="2" t="inlineStr">
@@ -16167,7 +16167,7 @@
       <c r="B136" s="2" t="inlineStr"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -16215,12 +16215,12 @@
       <c r="N136" s="2" t="inlineStr"/>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -16234,7 +16234,7 @@
       <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W136" s="2" t="inlineStr">
@@ -16259,7 +16259,7 @@
       </c>
       <c r="AA136" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB136" s="2" t="inlineStr">
@@ -16283,22 +16283,22 @@
       <c r="B137" s="2" t="inlineStr"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -16331,12 +16331,12 @@
       <c r="N137" s="2" t="inlineStr"/>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -16350,7 +16350,7 @@
       <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W137" s="2" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="AA137" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB137" s="2" t="inlineStr">
@@ -16399,7 +16399,7 @@
       <c r="B138" s="2" t="inlineStr"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -16447,12 +16447,12 @@
       <c r="N138" s="2" t="inlineStr"/>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -16466,7 +16466,7 @@
       <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W138" s="2" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="AA138" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB138" s="2" t="inlineStr">
@@ -16515,22 +16515,22 @@
       <c r="B139" s="2" t="inlineStr"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16563,12 +16563,12 @@
       <c r="N139" s="2" t="inlineStr"/>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -16582,7 +16582,7 @@
       <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W139" s="2" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="AA139" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB139" s="2" t="inlineStr">
@@ -16631,7 +16631,7 @@
       <c r="B140" s="2" t="inlineStr"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -16641,7 +16641,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -16679,12 +16679,12 @@
       <c r="N140" s="2" t="inlineStr"/>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -16698,7 +16698,7 @@
       <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W140" s="2" t="inlineStr">
@@ -16747,7 +16747,7 @@
       <c r="B141" s="2" t="inlineStr"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -16795,12 +16795,12 @@
       <c r="N141" s="2" t="inlineStr"/>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -16814,7 +16814,7 @@
       <c r="U141" s="2" t="inlineStr"/>
       <c r="V141" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W141" s="2" t="inlineStr">
@@ -16839,7 +16839,7 @@
       </c>
       <c r="AA141" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB141" s="2" t="inlineStr">
@@ -16863,7 +16863,7 @@
       <c r="B142" s="2" t="inlineStr"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -16873,7 +16873,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -16930,7 +16930,7 @@
       <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W142" s="2" t="inlineStr">
@@ -16979,7 +16979,7 @@
       <c r="B143" s="2" t="inlineStr"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -17027,12 +17027,12 @@
       <c r="N143" s="2" t="inlineStr"/>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -17046,7 +17046,7 @@
       <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W143" s="2" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="AA143" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB143" s="2" t="inlineStr">
@@ -17095,7 +17095,7 @@
       <c r="B144" s="2" t="inlineStr"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       <c r="N144" s="2" t="inlineStr"/>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -17162,7 +17162,7 @@
       <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W144" s="2" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="AA144" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB144" s="2" t="inlineStr">
@@ -17211,22 +17211,22 @@
       <c r="B145" s="2" t="inlineStr"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -17259,12 +17259,12 @@
       <c r="N145" s="2" t="inlineStr"/>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -17278,7 +17278,7 @@
       <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W145" s="2" t="inlineStr">
@@ -17327,22 +17327,22 @@
       <c r="B146" s="2" t="inlineStr"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -17375,12 +17375,12 @@
       <c r="N146" s="2" t="inlineStr"/>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -17394,7 +17394,7 @@
       <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W146" s="2" t="inlineStr">
@@ -17443,7 +17443,7 @@
       <c r="B147" s="2" t="inlineStr"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -17453,7 +17453,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -17491,12 +17491,12 @@
       <c r="N147" s="2" t="inlineStr"/>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -17510,7 +17510,7 @@
       <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W147" s="2" t="inlineStr">
@@ -17535,7 +17535,7 @@
       </c>
       <c r="AA147" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB147" s="2" t="inlineStr">
@@ -17559,22 +17559,22 @@
       <c r="B148" s="2" t="inlineStr"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -17626,7 +17626,7 @@
       <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="W148" s="2" t="inlineStr">
@@ -17675,22 +17675,22 @@
       <c r="B149" s="2" t="inlineStr"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -17723,12 +17723,12 @@
       <c r="N149" s="2" t="inlineStr"/>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -17742,7 +17742,7 @@
       <c r="U149" s="2" t="inlineStr"/>
       <c r="V149" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W149" s="2" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="AA149" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB149" s="2" t="inlineStr">
@@ -17791,22 +17791,22 @@
       <c r="B150" s="2" t="inlineStr"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -17839,12 +17839,12 @@
       <c r="N150" s="2" t="inlineStr"/>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -17858,7 +17858,7 @@
       <c r="U150" s="2" t="inlineStr"/>
       <c r="V150" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W150" s="2" t="inlineStr">
@@ -17883,7 +17883,7 @@
       </c>
       <c r="AA150" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB150" s="2" t="inlineStr">
@@ -17907,22 +17907,22 @@
       <c r="B151" s="2" t="inlineStr"/>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -17955,12 +17955,12 @@
       <c r="N151" s="2" t="inlineStr"/>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -17974,7 +17974,7 @@
       <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W151" s="2" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="AA151" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB151" s="2" t="inlineStr">
@@ -18023,22 +18023,22 @@
       <c r="B152" s="2" t="inlineStr"/>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -18090,7 +18090,7 @@
       <c r="U152" s="2" t="inlineStr"/>
       <c r="V152" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W152" s="2" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="AA152" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB152" s="2" t="inlineStr">
@@ -18139,22 +18139,22 @@
       <c r="B153" s="2" t="inlineStr"/>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -18192,7 +18192,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -18206,7 +18206,7 @@
       <c r="U153" s="2" t="inlineStr"/>
       <c r="V153" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W153" s="2" t="inlineStr">
@@ -18231,7 +18231,7 @@
       </c>
       <c r="AA153" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB153" s="2" t="inlineStr">
@@ -18255,7 +18255,7 @@
       <c r="B154" s="2" t="inlineStr"/>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -18303,12 +18303,12 @@
       <c r="N154" s="2" t="inlineStr"/>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -18322,7 +18322,7 @@
       <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="W154" s="2" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="AA154" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB154" s="2" t="inlineStr">
@@ -18371,7 +18371,7 @@
       <c r="B155" s="2" t="inlineStr"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -18438,7 +18438,7 @@
       <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W155" s="2" t="inlineStr">
@@ -18487,7 +18487,7 @@
       <c r="B156" s="2" t="inlineStr"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -18535,12 +18535,12 @@
       <c r="N156" s="2" t="inlineStr"/>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -18554,7 +18554,7 @@
       <c r="U156" s="2" t="inlineStr"/>
       <c r="V156" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W156" s="2" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="AA156" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB156" s="2" t="inlineStr">
@@ -18608,17 +18608,17 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -18656,7 +18656,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -18670,7 +18670,7 @@
       <c r="U157" s="2" t="inlineStr"/>
       <c r="V157" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W157" s="2" t="inlineStr">
@@ -18724,17 +18724,17 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -18786,7 +18786,7 @@
       <c r="U158" s="2" t="inlineStr"/>
       <c r="V158" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="W158" s="2" t="inlineStr">
@@ -18840,17 +18840,17 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -18888,7 +18888,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -18902,7 +18902,7 @@
       <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W159" s="2" t="inlineStr">
@@ -18956,17 +18956,17 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -19018,7 +19018,7 @@
       <c r="U160" s="2" t="inlineStr"/>
       <c r="V160" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="W160" s="2" t="inlineStr">
@@ -19053,6 +19053,1630 @@
       </c>
       <c r="AC160" s="2" t="inlineStr"/>
       <c r="AD160" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr"/>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr"/>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr"/>
+      <c r="S161" s="2" t="inlineStr"/>
+      <c r="T161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z161" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA161" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB161" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC161" s="2" t="inlineStr"/>
+      <c r="AD161" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr"/>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr"/>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr"/>
+      <c r="S162" s="2" t="inlineStr"/>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="W162" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X162" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y162" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z162" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA162" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB162" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC162" s="2" t="inlineStr"/>
+      <c r="AD162" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr"/>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr"/>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr"/>
+      <c r="S163" s="2" t="inlineStr"/>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z163" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA163" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB163" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC163" s="2" t="inlineStr"/>
+      <c r="AD163" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr"/>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr"/>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr"/>
+      <c r="S164" s="2" t="inlineStr"/>
+      <c r="T164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="W164" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X164" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y164" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z164" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA164" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB164" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC164" s="2" t="inlineStr"/>
+      <c r="AD164" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr"/>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr"/>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr"/>
+      <c r="S165" s="2" t="inlineStr"/>
+      <c r="T165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X165" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y165" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z165" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA165" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB165" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC165" s="2" t="inlineStr"/>
+      <c r="AD165" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr"/>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr"/>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr"/>
+      <c r="S166" s="2" t="inlineStr"/>
+      <c r="T166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="W166" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z166" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA166" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB166" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC166" s="2" t="inlineStr"/>
+      <c r="AD166" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr"/>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr"/>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr"/>
+      <c r="S167" s="2" t="inlineStr"/>
+      <c r="T167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z167" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA167" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB167" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC167" s="2" t="inlineStr"/>
+      <c r="AD167" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr"/>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr"/>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr"/>
+      <c r="S168" s="2" t="inlineStr"/>
+      <c r="T168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z168" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA168" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB168" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC168" s="2" t="inlineStr"/>
+      <c r="AD168" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr"/>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr"/>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr"/>
+      <c r="S169" s="2" t="inlineStr"/>
+      <c r="T169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z169" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA169" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB169" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC169" s="2" t="inlineStr"/>
+      <c r="AD169" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr"/>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr"/>
+      <c r="S170" s="2" t="inlineStr"/>
+      <c r="T170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X170" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y170" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z170" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA170" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB170" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC170" s="2" t="inlineStr"/>
+      <c r="AD170" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr"/>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr"/>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr"/>
+      <c r="S171" s="2" t="inlineStr"/>
+      <c r="T171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="W171" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z171" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA171" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB171" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC171" s="2" t="inlineStr"/>
+      <c r="AD171" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr"/>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr"/>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr"/>
+      <c r="S172" s="2" t="inlineStr"/>
+      <c r="T172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z172" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA172" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB172" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC172" s="2" t="inlineStr"/>
+      <c r="AD172" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr"/>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr"/>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr"/>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr"/>
+      <c r="S173" s="2" t="inlineStr"/>
+      <c r="T173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="W173" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X173" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y173" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z173" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA173" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB173" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AD173" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr"/>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr"/>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr"/>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr"/>
+      <c r="S174" s="2" t="inlineStr"/>
+      <c r="T174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z174" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA174" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB174" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC174" s="2" t="inlineStr"/>
+      <c r="AD174" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-29-operations.xlsx
+++ b/data/export/2026-10-29-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD174"/>
+  <dimension ref="A1:AD188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6417,28 +6417,28 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6490,7 +6490,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6526,35 +6526,35 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6642,35 +6642,35 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6758,35 +6758,35 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -6874,35 +6874,35 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6954,7 +6954,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -6990,7 +6990,7 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7070,7 +7070,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7186,7 +7186,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7467,22 +7467,22 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7583,7 +7583,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7699,7 +7699,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7815,7 +7815,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7882,7 +7882,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -7931,7 +7931,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8163,7 +8163,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8230,7 +8230,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8279,7 +8279,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8346,7 +8346,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8395,7 +8395,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8578,7 +8578,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8627,7 +8627,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8694,7 +8694,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8743,7 +8743,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8859,22 +8859,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8907,7 +8907,7 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -8975,22 +8975,22 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9139,12 +9139,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9207,22 +9207,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9274,7 +9274,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9323,22 +9323,22 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9371,12 +9371,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9555,7 +9555,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9671,22 +9671,22 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9738,7 +9738,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9787,22 +9787,22 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -9903,22 +9903,22 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9951,12 +9951,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
@@ -10019,22 +10019,22 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10086,7 +10086,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10135,22 +10135,22 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10202,7 +10202,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10318,7 +10318,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
@@ -10367,7 +10367,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10415,12 +10415,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10434,7 +10434,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10483,22 +10483,22 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10550,7 +10550,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
@@ -10599,22 +10599,22 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10666,7 +10666,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -10715,7 +10715,7 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -10831,22 +10831,22 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10898,7 +10898,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
@@ -10947,22 +10947,22 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11063,7 +11063,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
@@ -11295,22 +11295,22 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11362,7 +11362,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11411,22 +11411,22 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11527,22 +11527,22 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11575,12 +11575,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11594,7 +11594,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
@@ -11643,22 +11643,22 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11710,7 +11710,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -11759,22 +11759,22 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -11923,12 +11923,12 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -11942,7 +11942,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
@@ -11991,7 +11991,7 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -12039,12 +12039,12 @@
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12058,7 +12058,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12107,7 +12107,7 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12174,7 +12174,7 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -12223,7 +12223,7 @@
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -12271,12 +12271,12 @@
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
@@ -12339,7 +12339,7 @@
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -12387,12 +12387,12 @@
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12406,7 +12406,7 @@
       <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
@@ -12455,22 +12455,22 @@
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12503,12 +12503,12 @@
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12522,7 +12522,7 @@
       <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
@@ -12571,22 +12571,22 @@
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12638,7 +12638,7 @@
       <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
@@ -12687,22 +12687,22 @@
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -12735,12 +12735,12 @@
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
@@ -12803,22 +12803,22 @@
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>沪A79307D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12851,12 +12851,12 @@
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
           <t>11:31</t>
-        </is>
-      </c>
-      <c r="P107" s="2" t="inlineStr">
-        <is>
-          <t>12:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12870,7 +12870,7 @@
       <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AA107" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB107" s="2" t="inlineStr">
@@ -12919,7 +12919,7 @@
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -12967,12 +12967,12 @@
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12986,7 +12986,7 @@
       <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="AA108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB108" s="2" t="inlineStr">
@@ -13035,7 +13035,7 @@
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -13045,7 +13045,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13102,7 +13102,7 @@
       <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -13199,12 +13199,12 @@
       <c r="N110" s="2" t="inlineStr"/>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -13218,7 +13218,7 @@
       <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB110" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -13315,12 +13315,12 @@
       <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -13334,7 +13334,7 @@
       <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
@@ -13383,7 +13383,7 @@
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -13431,12 +13431,12 @@
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -13450,7 +13450,7 @@
       <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="W112" s="2" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="AA112" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB112" s="2" t="inlineStr">
@@ -13499,22 +13499,22 @@
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -13547,12 +13547,12 @@
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -13566,7 +13566,7 @@
       <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
@@ -13615,22 +13615,22 @@
       <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -13682,7 +13682,7 @@
       <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="W114" s="2" t="inlineStr">
@@ -13731,22 +13731,22 @@
       <c r="B115" s="2" t="inlineStr"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -13779,12 +13779,12 @@
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -13798,7 +13798,7 @@
       <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="AA115" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB115" s="2" t="inlineStr">
@@ -13847,22 +13847,22 @@
       <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -13914,7 +13914,7 @@
       <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="AA116" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB116" s="2" t="inlineStr">
@@ -13957,28 +13957,28 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -14011,7 +14011,7 @@
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
@@ -14030,7 +14030,7 @@
       <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
@@ -14066,35 +14066,35 @@
       <c r="AC117" s="2" t="inlineStr"/>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -14127,12 +14127,12 @@
       <c r="N118" s="2" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -14146,7 +14146,7 @@
       <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="W118" s="2" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="AA118" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB118" s="2" t="inlineStr">
@@ -14182,35 +14182,35 @@
       <c r="AC118" s="2" t="inlineStr"/>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr"/>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       <c r="N119" s="2" t="inlineStr"/>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -14262,7 +14262,7 @@
       <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="W119" s="2" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="AA119" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB119" s="2" t="inlineStr">
@@ -14298,35 +14298,35 @@
       <c r="AC119" s="2" t="inlineStr"/>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr"/>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -14359,12 +14359,12 @@
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -14378,7 +14378,7 @@
       <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="W120" s="2" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="AA120" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB120" s="2" t="inlineStr">
@@ -14414,35 +14414,35 @@
       <c r="AC120" s="2" t="inlineStr"/>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr"/>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -14475,12 +14475,12 @@
       <c r="N121" s="2" t="inlineStr"/>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -14494,7 +14494,7 @@
       <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="W121" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="AA121" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB121" s="2" t="inlineStr">
@@ -14530,35 +14530,35 @@
       <c r="AC121" s="2" t="inlineStr"/>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -14591,12 +14591,12 @@
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -14610,7 +14610,7 @@
       <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="W122" s="2" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="AA122" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB122" s="2" t="inlineStr">
@@ -14646,35 +14646,35 @@
       <c r="AC122" s="2" t="inlineStr"/>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -14707,12 +14707,12 @@
       <c r="N123" s="2" t="inlineStr"/>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -14726,7 +14726,7 @@
       <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="AA123" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB123" s="2" t="inlineStr">
@@ -14762,35 +14762,35 @@
       <c r="AC123" s="2" t="inlineStr"/>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -14823,12 +14823,12 @@
       <c r="N124" s="2" t="inlineStr"/>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -14842,7 +14842,7 @@
       <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="W124" s="2" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="AA124" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB124" s="2" t="inlineStr">
@@ -14878,35 +14878,35 @@
       <c r="AC124" s="2" t="inlineStr"/>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -14939,12 +14939,12 @@
       <c r="N125" s="2" t="inlineStr"/>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -14958,7 +14958,7 @@
       <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="W125" s="2" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="AA125" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB125" s="2" t="inlineStr">
@@ -14994,35 +14994,35 @@
       <c r="AC125" s="2" t="inlineStr"/>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -15060,7 +15060,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -15074,7 +15074,7 @@
       <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="W126" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       <c r="AC126" s="2" t="inlineStr"/>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -15123,7 +15123,7 @@
       <c r="B127" s="2" t="inlineStr"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -15133,7 +15133,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       <c r="N127" s="2" t="inlineStr"/>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -15190,7 +15190,7 @@
       <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W127" s="2" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="AA127" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB127" s="2" t="inlineStr">
@@ -15239,7 +15239,7 @@
       <c r="B128" s="2" t="inlineStr"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -15287,12 +15287,12 @@
       <c r="N128" s="2" t="inlineStr"/>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -15306,7 +15306,7 @@
       <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W128" s="2" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="AA128" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB128" s="2" t="inlineStr">
@@ -15355,22 +15355,22 @@
       <c r="B129" s="2" t="inlineStr"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -15403,12 +15403,12 @@
       <c r="N129" s="2" t="inlineStr"/>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -15422,7 +15422,7 @@
       <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W129" s="2" t="inlineStr">
@@ -15447,7 +15447,7 @@
       </c>
       <c r="AA129" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB129" s="2" t="inlineStr">
@@ -15471,22 +15471,22 @@
       <c r="B130" s="2" t="inlineStr"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -15519,12 +15519,12 @@
       <c r="N130" s="2" t="inlineStr"/>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -15538,7 +15538,7 @@
       <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="AA130" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB130" s="2" t="inlineStr">
@@ -15587,7 +15587,7 @@
       <c r="B131" s="2" t="inlineStr"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -15635,12 +15635,12 @@
       <c r="N131" s="2" t="inlineStr"/>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -15654,7 +15654,7 @@
       <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W131" s="2" t="inlineStr">
@@ -15679,7 +15679,7 @@
       </c>
       <c r="AA131" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB131" s="2" t="inlineStr">
@@ -15703,7 +15703,7 @@
       <c r="B132" s="2" t="inlineStr"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -15751,12 +15751,12 @@
       <c r="N132" s="2" t="inlineStr"/>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -15770,7 +15770,7 @@
       <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
@@ -15819,22 +15819,22 @@
       <c r="B133" s="2" t="inlineStr"/>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -15867,12 +15867,12 @@
       <c r="N133" s="2" t="inlineStr"/>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -15886,7 +15886,7 @@
       <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W133" s="2" t="inlineStr">
@@ -15911,7 +15911,7 @@
       </c>
       <c r="AA133" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB133" s="2" t="inlineStr">
@@ -15935,22 +15935,22 @@
       <c r="B134" s="2" t="inlineStr"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -15983,12 +15983,12 @@
       <c r="N134" s="2" t="inlineStr"/>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -16002,7 +16002,7 @@
       <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W134" s="2" t="inlineStr">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="AA134" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB134" s="2" t="inlineStr">
@@ -16051,22 +16051,22 @@
       <c r="B135" s="2" t="inlineStr"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>08:09</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -16099,12 +16099,12 @@
       <c r="N135" s="2" t="inlineStr"/>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -16118,7 +16118,7 @@
       <c r="U135" s="2" t="inlineStr"/>
       <c r="V135" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W135" s="2" t="inlineStr">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="AA135" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB135" s="2" t="inlineStr">
@@ -16167,22 +16167,22 @@
       <c r="B136" s="2" t="inlineStr"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -16215,12 +16215,12 @@
       <c r="N136" s="2" t="inlineStr"/>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -16234,7 +16234,7 @@
       <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W136" s="2" t="inlineStr">
@@ -16259,7 +16259,7 @@
       </c>
       <c r="AA136" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB136" s="2" t="inlineStr">
@@ -16283,7 +16283,7 @@
       <c r="B137" s="2" t="inlineStr"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -16331,12 +16331,12 @@
       <c r="N137" s="2" t="inlineStr"/>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -16350,7 +16350,7 @@
       <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W137" s="2" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="AA137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB137" s="2" t="inlineStr">
@@ -16399,22 +16399,22 @@
       <c r="B138" s="2" t="inlineStr"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -16447,7 +16447,7 @@
       <c r="N138" s="2" t="inlineStr"/>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
@@ -16466,7 +16466,7 @@
       <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W138" s="2" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="AA138" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB138" s="2" t="inlineStr">
@@ -16515,7 +16515,7 @@
       <c r="B139" s="2" t="inlineStr"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -16563,12 +16563,12 @@
       <c r="N139" s="2" t="inlineStr"/>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -16582,7 +16582,7 @@
       <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W139" s="2" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="AA139" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB139" s="2" t="inlineStr">
@@ -16631,22 +16631,22 @@
       <c r="B140" s="2" t="inlineStr"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16679,12 +16679,12 @@
       <c r="N140" s="2" t="inlineStr"/>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -16698,7 +16698,7 @@
       <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W140" s="2" t="inlineStr">
@@ -16747,22 +16747,22 @@
       <c r="B141" s="2" t="inlineStr"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -16795,12 +16795,12 @@
       <c r="N141" s="2" t="inlineStr"/>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -16814,7 +16814,7 @@
       <c r="U141" s="2" t="inlineStr"/>
       <c r="V141" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W141" s="2" t="inlineStr">
@@ -16839,7 +16839,7 @@
       </c>
       <c r="AA141" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB141" s="2" t="inlineStr">
@@ -16863,22 +16863,22 @@
       <c r="B142" s="2" t="inlineStr"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16911,12 +16911,12 @@
       <c r="N142" s="2" t="inlineStr"/>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -16930,7 +16930,7 @@
       <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W142" s="2" t="inlineStr">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="AA142" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB142" s="2" t="inlineStr">
@@ -16979,22 +16979,22 @@
       <c r="B143" s="2" t="inlineStr"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -17027,12 +17027,12 @@
       <c r="N143" s="2" t="inlineStr"/>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -17046,7 +17046,7 @@
       <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="W143" s="2" t="inlineStr">
@@ -17095,22 +17095,22 @@
       <c r="B144" s="2" t="inlineStr"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A53062D</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       <c r="N144" s="2" t="inlineStr"/>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -17162,7 +17162,7 @@
       <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W144" s="2" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="AA144" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB144" s="2" t="inlineStr">
@@ -17211,22 +17211,22 @@
       <c r="B145" s="2" t="inlineStr"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -17259,12 +17259,12 @@
       <c r="N145" s="2" t="inlineStr"/>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -17278,7 +17278,7 @@
       <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="W145" s="2" t="inlineStr">
@@ -17303,7 +17303,7 @@
       </c>
       <c r="AA145" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB145" s="2" t="inlineStr">
@@ -17327,22 +17327,22 @@
       <c r="B146" s="2" t="inlineStr"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -17375,12 +17375,12 @@
       <c r="N146" s="2" t="inlineStr"/>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -17394,7 +17394,7 @@
       <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W146" s="2" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="AA146" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB146" s="2" t="inlineStr">
@@ -17443,22 +17443,22 @@
       <c r="B147" s="2" t="inlineStr"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -17491,12 +17491,12 @@
       <c r="N147" s="2" t="inlineStr"/>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -17510,7 +17510,7 @@
       <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W147" s="2" t="inlineStr">
@@ -17535,7 +17535,7 @@
       </c>
       <c r="AA147" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB147" s="2" t="inlineStr">
@@ -17559,22 +17559,22 @@
       <c r="B148" s="2" t="inlineStr"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       <c r="N148" s="2" t="inlineStr"/>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -17626,7 +17626,7 @@
       <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W148" s="2" t="inlineStr">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="AA148" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB148" s="2" t="inlineStr">
@@ -17675,7 +17675,7 @@
       <c r="B149" s="2" t="inlineStr"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -17723,12 +17723,12 @@
       <c r="N149" s="2" t="inlineStr"/>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -17742,7 +17742,7 @@
       <c r="U149" s="2" t="inlineStr"/>
       <c r="V149" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W149" s="2" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="AA149" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB149" s="2" t="inlineStr">
@@ -17791,22 +17791,22 @@
       <c r="B150" s="2" t="inlineStr"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -17839,12 +17839,12 @@
       <c r="N150" s="2" t="inlineStr"/>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -17858,7 +17858,7 @@
       <c r="U150" s="2" t="inlineStr"/>
       <c r="V150" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W150" s="2" t="inlineStr">
@@ -17883,7 +17883,7 @@
       </c>
       <c r="AA150" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB150" s="2" t="inlineStr">
@@ -17907,22 +17907,22 @@
       <c r="B151" s="2" t="inlineStr"/>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -17974,7 +17974,7 @@
       <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W151" s="2" t="inlineStr">
@@ -18023,22 +18023,22 @@
       <c r="B152" s="2" t="inlineStr"/>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -18071,12 +18071,12 @@
       <c r="N152" s="2" t="inlineStr"/>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -18090,7 +18090,7 @@
       <c r="U152" s="2" t="inlineStr"/>
       <c r="V152" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W152" s="2" t="inlineStr">
@@ -18139,22 +18139,22 @@
       <c r="B153" s="2" t="inlineStr"/>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -18187,12 +18187,12 @@
       <c r="N153" s="2" t="inlineStr"/>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -18206,7 +18206,7 @@
       <c r="U153" s="2" t="inlineStr"/>
       <c r="V153" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W153" s="2" t="inlineStr">
@@ -18255,7 +18255,7 @@
       <c r="B154" s="2" t="inlineStr"/>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -18303,12 +18303,12 @@
       <c r="N154" s="2" t="inlineStr"/>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -18322,7 +18322,7 @@
       <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W154" s="2" t="inlineStr">
@@ -18347,7 +18347,7 @@
       </c>
       <c r="AA154" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB154" s="2" t="inlineStr">
@@ -18371,7 +18371,7 @@
       <c r="B155" s="2" t="inlineStr"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -18419,12 +18419,12 @@
       <c r="N155" s="2" t="inlineStr"/>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -18438,7 +18438,7 @@
       <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W155" s="2" t="inlineStr">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="AA155" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB155" s="2" t="inlineStr">
@@ -18487,7 +18487,7 @@
       <c r="B156" s="2" t="inlineStr"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -18535,12 +18535,12 @@
       <c r="N156" s="2" t="inlineStr"/>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -18554,7 +18554,7 @@
       <c r="U156" s="2" t="inlineStr"/>
       <c r="V156" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W156" s="2" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="AA156" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB156" s="2" t="inlineStr">
@@ -18603,7 +18603,7 @@
       <c r="B157" s="2" t="inlineStr"/>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -18651,12 +18651,12 @@
       <c r="N157" s="2" t="inlineStr"/>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -18670,7 +18670,7 @@
       <c r="U157" s="2" t="inlineStr"/>
       <c r="V157" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W157" s="2" t="inlineStr">
@@ -18719,7 +18719,7 @@
       <c r="B158" s="2" t="inlineStr"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -18729,7 +18729,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -18772,7 +18772,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -18786,7 +18786,7 @@
       <c r="U158" s="2" t="inlineStr"/>
       <c r="V158" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="W158" s="2" t="inlineStr">
@@ -18835,7 +18835,7 @@
       <c r="B159" s="2" t="inlineStr"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -18883,12 +18883,12 @@
       <c r="N159" s="2" t="inlineStr"/>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -18902,7 +18902,7 @@
       <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W159" s="2" t="inlineStr">
@@ -18927,7 +18927,7 @@
       </c>
       <c r="AA159" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB159" s="2" t="inlineStr">
@@ -18951,7 +18951,7 @@
       <c r="B160" s="2" t="inlineStr"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -18961,7 +18961,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -18999,12 +18999,12 @@
       <c r="N160" s="2" t="inlineStr"/>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -19018,7 +19018,7 @@
       <c r="U160" s="2" t="inlineStr"/>
       <c r="V160" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W160" s="2" t="inlineStr">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="AA160" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB160" s="2" t="inlineStr">
@@ -19067,7 +19067,7 @@
       <c r="B161" s="2" t="inlineStr"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -19115,12 +19115,12 @@
       <c r="N161" s="2" t="inlineStr"/>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -19134,7 +19134,7 @@
       <c r="U161" s="2" t="inlineStr"/>
       <c r="V161" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W161" s="2" t="inlineStr">
@@ -19183,7 +19183,7 @@
       <c r="B162" s="2" t="inlineStr"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -19193,7 +19193,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -19231,12 +19231,12 @@
       <c r="N162" s="2" t="inlineStr"/>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -19250,7 +19250,7 @@
       <c r="U162" s="2" t="inlineStr"/>
       <c r="V162" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W162" s="2" t="inlineStr">
@@ -19299,7 +19299,7 @@
       <c r="B163" s="2" t="inlineStr"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -19309,7 +19309,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -19347,12 +19347,12 @@
       <c r="N163" s="2" t="inlineStr"/>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -19366,7 +19366,7 @@
       <c r="U163" s="2" t="inlineStr"/>
       <c r="V163" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W163" s="2" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="AA163" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB163" s="2" t="inlineStr">
@@ -19420,17 +19420,17 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -19482,7 +19482,7 @@
       <c r="U164" s="2" t="inlineStr"/>
       <c r="V164" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="W164" s="2" t="inlineStr">
@@ -19536,17 +19536,17 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -19584,7 +19584,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -19598,7 +19598,7 @@
       <c r="U165" s="2" t="inlineStr"/>
       <c r="V165" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W165" s="2" t="inlineStr">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="AA165" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB165" s="2" t="inlineStr">
@@ -19647,22 +19647,22 @@
       <c r="B166" s="2" t="inlineStr"/>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -19695,12 +19695,12 @@
       <c r="N166" s="2" t="inlineStr"/>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -19714,7 +19714,7 @@
       <c r="U166" s="2" t="inlineStr"/>
       <c r="V166" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W166" s="2" t="inlineStr">
@@ -19739,7 +19739,7 @@
       </c>
       <c r="AA166" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB166" s="2" t="inlineStr">
@@ -19763,7 +19763,7 @@
       <c r="B167" s="2" t="inlineStr"/>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -19816,7 +19816,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -19830,7 +19830,7 @@
       <c r="U167" s="2" t="inlineStr"/>
       <c r="V167" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W167" s="2" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="AA167" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB167" s="2" t="inlineStr">
@@ -19879,7 +19879,7 @@
       <c r="B168" s="2" t="inlineStr"/>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -19946,7 +19946,7 @@
       <c r="U168" s="2" t="inlineStr"/>
       <c r="V168" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="W168" s="2" t="inlineStr">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="AA168" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB168" s="2" t="inlineStr">
@@ -19995,7 +19995,7 @@
       <c r="B169" s="2" t="inlineStr"/>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -20005,7 +20005,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -20043,12 +20043,12 @@
       <c r="N169" s="2" t="inlineStr"/>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -20062,7 +20062,7 @@
       <c r="U169" s="2" t="inlineStr"/>
       <c r="V169" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W169" s="2" t="inlineStr">
@@ -20111,7 +20111,7 @@
       <c r="B170" s="2" t="inlineStr"/>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -20121,7 +20121,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -20159,7 +20159,7 @@
       <c r="N170" s="2" t="inlineStr"/>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
@@ -20178,7 +20178,7 @@
       <c r="U170" s="2" t="inlineStr"/>
       <c r="V170" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="W170" s="2" t="inlineStr">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="AA170" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB170" s="2" t="inlineStr">
@@ -20227,7 +20227,7 @@
       <c r="B171" s="2" t="inlineStr"/>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -20237,7 +20237,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -20275,12 +20275,12 @@
       <c r="N171" s="2" t="inlineStr"/>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -20294,7 +20294,7 @@
       <c r="U171" s="2" t="inlineStr"/>
       <c r="V171" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="W171" s="2" t="inlineStr">
@@ -20343,7 +20343,7 @@
       <c r="B172" s="2" t="inlineStr"/>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -20353,7 +20353,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -20391,12 +20391,12 @@
       <c r="N172" s="2" t="inlineStr"/>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -20410,7 +20410,7 @@
       <c r="U172" s="2" t="inlineStr"/>
       <c r="V172" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="W172" s="2" t="inlineStr">
@@ -20459,22 +20459,22 @@
       <c r="B173" s="2" t="inlineStr"/>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -20512,7 +20512,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -20526,7 +20526,7 @@
       <c r="U173" s="2" t="inlineStr"/>
       <c r="V173" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="W173" s="2" t="inlineStr">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="AA173" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB173" s="2" t="inlineStr">
@@ -20580,17 +20580,17 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -20642,7 +20642,7 @@
       <c r="U174" s="2" t="inlineStr"/>
       <c r="V174" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="W174" s="2" t="inlineStr">
@@ -20677,6 +20677,1630 @@
       </c>
       <c r="AC174" s="2" t="inlineStr"/>
       <c r="AD174" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr"/>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr"/>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R175" s="2" t="inlineStr"/>
+      <c r="S175" s="2" t="inlineStr"/>
+      <c r="T175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z175" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA175" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB175" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC175" s="2" t="inlineStr"/>
+      <c r="AD175" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr"/>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr"/>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr"/>
+      <c r="S176" s="2" t="inlineStr"/>
+      <c r="T176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="W176" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X176" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y176" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z176" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA176" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB176" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC176" s="2" t="inlineStr"/>
+      <c r="AD176" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr"/>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr"/>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr"/>
+      <c r="S177" s="2" t="inlineStr"/>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z177" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA177" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB177" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC177" s="2" t="inlineStr"/>
+      <c r="AD177" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr"/>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr"/>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr"/>
+      <c r="S178" s="2" t="inlineStr"/>
+      <c r="T178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z178" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA178" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB178" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC178" s="2" t="inlineStr"/>
+      <c r="AD178" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr"/>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr"/>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr"/>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr"/>
+      <c r="S179" s="2" t="inlineStr"/>
+      <c r="T179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="W179" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X179" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y179" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z179" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA179" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB179" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC179" s="2" t="inlineStr"/>
+      <c r="AD179" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr"/>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr"/>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R180" s="2" t="inlineStr"/>
+      <c r="S180" s="2" t="inlineStr"/>
+      <c r="T180" s="2" t="inlineStr"/>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="W180" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X180" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y180" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z180" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA180" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB180" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC180" s="2" t="inlineStr"/>
+      <c r="AD180" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr"/>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr"/>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr"/>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="inlineStr"/>
+      <c r="S181" s="2" t="inlineStr"/>
+      <c r="T181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="W181" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y181" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z181" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA181" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB181" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC181" s="2" t="inlineStr"/>
+      <c r="AD181" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr"/>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr"/>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="inlineStr"/>
+      <c r="S182" s="2" t="inlineStr"/>
+      <c r="T182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="W182" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X182" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y182" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z182" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA182" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB182" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC182" s="2" t="inlineStr"/>
+      <c r="AD182" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr"/>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr"/>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr"/>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr"/>
+      <c r="S183" s="2" t="inlineStr"/>
+      <c r="T183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="W183" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X183" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y183" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z183" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA183" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB183" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC183" s="2" t="inlineStr"/>
+      <c r="AD183" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr"/>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr"/>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr"/>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr"/>
+      <c r="S184" s="2" t="inlineStr"/>
+      <c r="T184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="W184" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X184" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y184" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z184" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA184" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB184" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC184" s="2" t="inlineStr"/>
+      <c r="AD184" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr"/>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr"/>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr"/>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R185" s="2" t="inlineStr"/>
+      <c r="S185" s="2" t="inlineStr"/>
+      <c r="T185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="W185" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X185" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y185" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z185" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA185" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB185" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC185" s="2" t="inlineStr"/>
+      <c r="AD185" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr"/>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr"/>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr"/>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R186" s="2" t="inlineStr"/>
+      <c r="S186" s="2" t="inlineStr"/>
+      <c r="T186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="W186" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X186" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y186" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z186" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA186" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB186" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC186" s="2" t="inlineStr"/>
+      <c r="AD186" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr"/>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr"/>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr"/>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="inlineStr"/>
+      <c r="S187" s="2" t="inlineStr"/>
+      <c r="T187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="W187" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X187" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y187" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z187" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA187" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB187" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC187" s="2" t="inlineStr"/>
+      <c r="AD187" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr"/>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K188" s="2" t="inlineStr"/>
+      <c r="L188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr"/>
+      <c r="O188" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R188" s="2" t="inlineStr"/>
+      <c r="S188" s="2" t="inlineStr"/>
+      <c r="T188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="W188" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X188" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y188" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z188" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA188" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB188" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC188" s="2" t="inlineStr"/>
+      <c r="AD188" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-29-operations.xlsx
+++ b/data/export/2026-10-29-operations.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1445,12 +1445,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2156,17 +2156,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3712,17 +3712,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4672,17 +4672,17 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6596,17 +6596,17 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7092,17 +7092,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7460,17 +7460,17 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8200,17 +8200,17 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8570,7 @@
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9061,12 +9061,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9552,17 +9552,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9916,17 +9916,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -10465,24 +10465,24 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -10579,32 +10579,36 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -10612,7 +10616,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10636,17 +10640,17 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10656,17 +10660,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -10709,12 +10713,12 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
@@ -10736,7 +10740,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10785,12 +10789,12 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -10823,32 +10827,36 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10856,7 +10864,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10880,17 +10888,17 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10900,17 +10908,17 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10984,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11096,7 +11104,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11145,12 +11153,12 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11224,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11265,12 +11273,12 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11344,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11380,17 +11388,17 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11518,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11638,7 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11758,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11940,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11986,7 +11994,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12106,7 +12114,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12234,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12412,7 +12420,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12456,17 +12464,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -12532,7 +12540,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12586,7 +12594,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12714,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12888,7 +12896,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12932,17 +12940,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13016,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13062,7 +13070,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -13128,7 +13136,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13182,7 +13190,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13256,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13484,7 +13492,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13538,7 +13546,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -13604,7 +13612,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13658,7 +13666,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13732,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -13768,13 +13776,17 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC110" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13972,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14014,7 +14026,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14092,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14134,7 +14146,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -14254,7 +14266,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14332,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14364,17 +14376,17 @@
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -14560,7 +14572,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14614,7 +14626,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14746,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -14800,7 +14812,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -14844,17 +14856,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -14974,7 +14986,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -15094,7 +15106,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -15330,7 +15342,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -15396,7 +15408,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15450,7 +15462,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -15570,7 +15582,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -15756,7 +15768,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -15800,17 +15812,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15888,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -15930,7 +15942,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -15996,7 +16008,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16040,17 +16052,17 @@
       </c>
       <c r="AB129" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC129" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -16232,7 +16244,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16352,7 +16364,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16406,7 +16418,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -16472,7 +16484,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16526,7 +16538,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -16708,7 +16720,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -16762,7 +16774,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16840,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -16872,13 +16884,17 @@
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC136" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC136" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -17064,7 +17080,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17118,7 +17134,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -17304,7 +17320,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17358,7 +17374,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -17478,7 +17494,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17614,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -17838,7 +17854,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -17904,7 +17920,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18074,7 +18090,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -18260,7 +18276,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18314,7 +18330,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -18500,7 +18516,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -18748,7 +18764,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -18802,7 +18818,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -19050,7 +19066,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -19174,7 +19190,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -19298,7 +19314,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -19546,7 +19562,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19686,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -19740,7 +19756,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -19784,17 +19800,17 @@
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -19992,7 +20008,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20112,7 +20128,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20166,7 +20182,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -20236,7 +20252,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -20280,17 +20296,17 @@
       </c>
       <c r="AB164" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC164" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -20360,7 +20376,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -20404,17 +20420,17 @@
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC165" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -20484,7 +20500,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -20538,7 +20554,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -20608,7 +20624,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -20662,7 +20678,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20748,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -20786,7 +20802,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20872,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -20900,17 +20916,17 @@
       </c>
       <c r="AB169" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -20980,7 +20996,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21034,7 +21050,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -21104,7 +21120,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21158,7 +21174,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -21282,7 +21298,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -21352,7 +21368,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21406,7 +21422,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -21530,7 +21546,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -21654,7 +21670,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -21840,7 +21856,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -21894,7 +21910,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -22134,7 +22150,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -22258,7 +22274,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -22498,7 +22514,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -22531,32 +22547,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -22564,7 +22584,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -22588,17 +22608,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -22608,13 +22628,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC183" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC183" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -22669,12 +22693,12 @@
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N184" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O184" s="2" t="inlineStr">
@@ -22684,7 +22708,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -22738,7 +22762,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22828,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -22891,32 +22915,36 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N186" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
           <t>08:02</t>
@@ -22924,7 +22952,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -22948,17 +22976,17 @@
       </c>
       <c r="X186" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z186" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA186" s="2" t="inlineStr">
@@ -22968,17 +22996,17 @@
       </c>
       <c r="AB186" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -23011,32 +23039,36 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N187" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -23044,7 +23076,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23068,17 +23100,17 @@
       </c>
       <c r="X187" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA187" s="2" t="inlineStr">
@@ -23088,17 +23120,17 @@
       </c>
       <c r="AB187" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC187" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -23136,7 +23168,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq31，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq53，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -23164,7 +23196,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23234,7 +23266,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -23267,32 +23299,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23300,7 +23336,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23324,17 +23360,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23344,17 +23380,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -23387,32 +23423,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23420,7 +23460,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23444,17 +23484,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23464,17 +23504,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -23540,7 +23580,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -23594,7 +23634,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -23627,12 +23667,12 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq48，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -23660,7 +23700,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -23668,10 +23708,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R192" s="2" t="inlineStr"/>
-      <c r="S192" s="2" t="inlineStr"/>
-      <c r="T192" s="2" t="inlineStr"/>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="R192" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V192" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -23714,7 +23770,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -23780,7 +23836,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -23834,7 +23890,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -23900,7 +23956,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -23954,7 +24010,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24076,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24074,7 +24130,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -24140,7 +24196,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24194,7 +24250,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -24260,7 +24316,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24314,7 +24370,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -24380,7 +24436,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24424,13 +24480,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC198" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC198" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -24496,7 +24556,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -24540,12 +24600,12 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
@@ -24976,7 +25036,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25025,12 +25085,12 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -25096,7 +25156,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25150,7 +25210,7 @@
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -25390,7 +25450,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25516,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -25500,17 +25560,17 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -25576,7 +25636,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -25620,17 +25680,17 @@
       </c>
       <c r="AB208" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC208" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -25750,7 +25810,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -25990,7 +26050,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26110,7 +26170,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -26230,7 +26290,7 @@
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -26296,7 +26356,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26340,17 +26400,17 @@
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -26416,7 +26476,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -26460,12 +26520,12 @@
       </c>
       <c r="AB215" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC215" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD215" s="2" t="inlineStr">
@@ -26590,7 +26650,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -26896,7 +26956,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -26945,12 +27005,12 @@
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -27252,7 +27312,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27306,7 +27366,7 @@
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -27426,7 +27486,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -27612,7 +27672,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -27656,17 +27716,17 @@
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -27732,7 +27792,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -27776,17 +27836,17 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27906,7 +27966,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28026,7 +28086,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -28266,7 +28326,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -28332,7 +28392,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28376,17 +28436,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -28812,7 +28872,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -28861,12 +28921,12 @@
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -28986,7 +29046,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29232,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29216,17 +29276,17 @@
       </c>
       <c r="AB238" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC238" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -29346,7 +29406,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -29466,7 +29526,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -29586,7 +29646,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -30186,7 +30246,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -30426,7 +30486,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -30546,7 +30606,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -30666,7 +30726,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -31232,7 +31292,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -31276,12 +31336,12 @@
       </c>
       <c r="AB255" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
@@ -31410,7 +31470,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -31530,7 +31590,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -31778,7 +31838,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -31902,7 +31962,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -32026,7 +32086,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -32096,7 +32156,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32150,7 +32210,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -32216,7 +32276,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32260,17 +32320,17 @@
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -32394,7 +32454,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -32588,7 +32648,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -32637,12 +32697,12 @@
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -32712,7 +32772,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -32756,17 +32816,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -33084,7 +33144,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33128,17 +33188,17 @@
       </c>
       <c r="AB270" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -33382,7 +33442,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -33452,7 +33512,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -33496,12 +33556,12 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
@@ -33750,7 +33810,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -33874,7 +33934,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -33998,7 +34058,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -34122,7 +34182,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -34192,7 +34252,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34246,7 +34306,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -34316,7 +34376,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -34360,17 +34420,17 @@
       </c>
       <c r="AB280" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -34494,7 +34554,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -34684,7 +34744,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -34733,12 +34793,12 @@
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -34808,7 +34868,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -34852,17 +34912,17 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -35230,7 +35290,7 @@
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -35300,7 +35360,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -35344,17 +35404,17 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35598,7 +35658,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -35664,7 +35724,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -35708,12 +35768,12 @@
       </c>
       <c r="AB291" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
@@ -35838,7 +35898,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -35962,7 +36022,7 @@
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36086,7 +36146,7 @@
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -36156,7 +36216,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36210,7 +36270,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -36253,24 +36313,24 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr"/>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N296" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O296" s="2" t="inlineStr">
@@ -36280,7 +36340,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -36329,12 +36389,12 @@
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -36367,32 +36427,36 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr"/>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N297" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N297" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O297" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -36400,7 +36464,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -36424,17 +36488,17 @@
       </c>
       <c r="X297" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z297" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA297" s="2" t="inlineStr">
@@ -36444,17 +36508,17 @@
       </c>
       <c r="AB297" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -36487,32 +36551,36 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr"/>
       <c r="M298" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N298" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O298" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -36520,7 +36588,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -36544,17 +36612,17 @@
       </c>
       <c r="X298" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z298" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA298" s="2" t="inlineStr">
@@ -36564,17 +36632,17 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36607,32 +36675,36 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr"/>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N299" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N299" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O299" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -36640,7 +36712,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -36664,17 +36736,17 @@
       </c>
       <c r="X299" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z299" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA299" s="2" t="inlineStr">
@@ -36684,17 +36756,17 @@
       </c>
       <c r="AB299" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -36727,32 +36799,36 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr"/>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N300" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O300" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -36760,7 +36836,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -36784,17 +36860,17 @@
       </c>
       <c r="X300" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y300" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z300" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA300" s="2" t="inlineStr">
@@ -36804,12 +36880,12 @@
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
@@ -36880,7 +36956,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -36934,7 +37010,7 @@
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -37000,7 +37076,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37044,17 +37120,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37120,7 +37196,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37164,17 +37240,17 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
